--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/125.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/125.xlsx
@@ -426,13 +426,13 @@
         <v>-13.93280603983048</v>
       </c>
       <c r="E2">
-        <v>-22.88643422170278</v>
+        <v>-23.56557852558112</v>
       </c>
       <c r="F2">
-        <v>-3.551595565523887</v>
+        <v>-3.680641124634203</v>
       </c>
       <c r="G2">
-        <v>-13.13794416035805</v>
+        <v>-14.45639043991881</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.6225843834169</v>
       </c>
       <c r="E3">
-        <v>-23.16814153277194</v>
+        <v>-23.59541211234366</v>
       </c>
       <c r="F3">
-        <v>-3.580713508099693</v>
+        <v>-3.222343545565765</v>
       </c>
       <c r="G3">
-        <v>-13.6041252515616</v>
+        <v>-13.36140267371332</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.23223303490738</v>
       </c>
       <c r="E4">
-        <v>-24.09243477705552</v>
+        <v>-24.92950961195136</v>
       </c>
       <c r="F4">
-        <v>-3.533542954714678</v>
+        <v>-3.488843421292214</v>
       </c>
       <c r="G4">
-        <v>-13.09985633392873</v>
+        <v>-13.43467828867954</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.78992961438981</v>
       </c>
       <c r="E5">
-        <v>-23.90941197156151</v>
+        <v>-25.44243174890415</v>
       </c>
       <c r="F5">
-        <v>-3.58009720275201</v>
+        <v>-3.50018708450615</v>
       </c>
       <c r="G5">
-        <v>-13.56953998231283</v>
+        <v>-14.15840823592901</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.2969632861912</v>
       </c>
       <c r="E6">
-        <v>-24.50381494133431</v>
+        <v>-24.90557209834681</v>
       </c>
       <c r="F6">
-        <v>-3.374576765015244</v>
+        <v>-3.372192723629987</v>
       </c>
       <c r="G6">
-        <v>-14.18920789635362</v>
+        <v>-13.3778395323158</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.75647847188243</v>
       </c>
       <c r="E7">
-        <v>-24.69738456279218</v>
+        <v>-26.08151717171063</v>
       </c>
       <c r="F7">
-        <v>-3.163334793627342</v>
+        <v>-3.508665424873803</v>
       </c>
       <c r="G7">
-        <v>-13.44251766051654</v>
+        <v>-13.73200997047088</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.18286707115248</v>
       </c>
       <c r="E8">
-        <v>-25.15951986374895</v>
+        <v>-26.94324501910424</v>
       </c>
       <c r="F8">
-        <v>-3.026420572557834</v>
+        <v>-3.460734430213018</v>
       </c>
       <c r="G8">
-        <v>-13.61087214337064</v>
+        <v>-13.77890715858019</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.58980903575916</v>
       </c>
       <c r="E9">
-        <v>-25.71725577948165</v>
+        <v>-26.55523178070501</v>
       </c>
       <c r="F9">
-        <v>-3.235915517093232</v>
+        <v>-3.183783871332851</v>
       </c>
       <c r="G9">
-        <v>-12.93917900618021</v>
+        <v>-13.45941468494898</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.979157648785733</v>
       </c>
       <c r="E10">
-        <v>-26.10314516357127</v>
+        <v>-27.12207445766714</v>
       </c>
       <c r="F10">
-        <v>-3.073784963915104</v>
+        <v>-3.4982785260101</v>
       </c>
       <c r="G10">
-        <v>-13.4585903591097</v>
+        <v>-13.11075133929848</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.372351686510754</v>
       </c>
       <c r="E11">
-        <v>-27.48977296166795</v>
+        <v>-28.54303714568997</v>
       </c>
       <c r="F11">
-        <v>-3.146783184552005</v>
+        <v>-3.460707094088725</v>
       </c>
       <c r="G11">
-        <v>-12.63373483254489</v>
+        <v>-13.02656416623481</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.784439547022975</v>
       </c>
       <c r="E12">
-        <v>-27.46080884191489</v>
+        <v>-29.2033429976964</v>
       </c>
       <c r="F12">
-        <v>-3.198891636025108</v>
+        <v>-3.46782194171137</v>
       </c>
       <c r="G12">
-        <v>-12.08684595163945</v>
+        <v>-12.07681168810992</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.22236818452574</v>
       </c>
       <c r="E13">
-        <v>-28.32917543220373</v>
+        <v>-29.66706779302986</v>
       </c>
       <c r="F13">
-        <v>-3.072351888308261</v>
+        <v>-3.2899664901259</v>
       </c>
       <c r="G13">
-        <v>-12.05523686283049</v>
+        <v>-12.8152917710096</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.708119797176613</v>
       </c>
       <c r="E14">
-        <v>-28.56586518316264</v>
+        <v>-30.30448673740153</v>
       </c>
       <c r="F14">
-        <v>-3.053413752745459</v>
+        <v>-3.425691175604987</v>
       </c>
       <c r="G14">
-        <v>-12.02552140606999</v>
+        <v>-12.00160933563983</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.251212400883094</v>
       </c>
       <c r="E15">
-        <v>-30.09017670498853</v>
+        <v>-32.03404681515106</v>
       </c>
       <c r="F15">
-        <v>-3.047991259726734</v>
+        <v>-3.027448576504709</v>
       </c>
       <c r="G15">
-        <v>-11.07554050030289</v>
+        <v>-12.16527277546478</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.848025445401899</v>
       </c>
       <c r="E16">
-        <v>-30.25826007473123</v>
+        <v>-32.11288981186161</v>
       </c>
       <c r="F16">
-        <v>-2.713834476376635</v>
+        <v>-2.671607619651528</v>
       </c>
       <c r="G16">
-        <v>-10.87309401948538</v>
+        <v>-11.03396997996626</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.503441874035683</v>
       </c>
       <c r="E17">
-        <v>-31.05432957748761</v>
+        <v>-32.45623871112318</v>
       </c>
       <c r="F17">
-        <v>-2.815749346310461</v>
+        <v>-2.830459494649375</v>
       </c>
       <c r="G17">
-        <v>-10.54680665113481</v>
+        <v>-10.54080132152657</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.210354612802854</v>
       </c>
       <c r="E18">
-        <v>-32.20593636729721</v>
+        <v>-32.59058268527173</v>
       </c>
       <c r="F18">
-        <v>-2.567994596541963</v>
+        <v>-2.556857196811323</v>
       </c>
       <c r="G18">
-        <v>-10.11266170911478</v>
+        <v>-10.58738400780965</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.954356838586625</v>
       </c>
       <c r="E19">
-        <v>-32.63135706523679</v>
+        <v>-33.89135740889399</v>
       </c>
       <c r="F19">
-        <v>-2.290106325761827</v>
+        <v>-2.612577330160632</v>
       </c>
       <c r="G19">
-        <v>-9.798428037072702</v>
+        <v>-9.802496697540466</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.732638625656795</v>
       </c>
       <c r="E20">
-        <v>-33.84395107874469</v>
+        <v>-34.92487744624258</v>
       </c>
       <c r="F20">
-        <v>-2.432713915990775</v>
+        <v>-2.374927005971482</v>
       </c>
       <c r="G20">
-        <v>-9.172877283608635</v>
+        <v>-9.674918204093572</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.537856404578606</v>
       </c>
       <c r="E21">
-        <v>-33.91370769235885</v>
+        <v>-35.18547301148797</v>
       </c>
       <c r="F21">
-        <v>-2.068636502051559</v>
+        <v>-2.055026425623563</v>
       </c>
       <c r="G21">
-        <v>-9.350137133963372</v>
+        <v>-9.280873900190739</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.360930326531233</v>
       </c>
       <c r="E22">
-        <v>-34.0627488288993</v>
+        <v>-36.07247200808138</v>
       </c>
       <c r="F22">
-        <v>-2.090859114366462</v>
+        <v>-2.283715471249228</v>
       </c>
       <c r="G22">
-        <v>-9.091722570258941</v>
+        <v>-9.366656756204335</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.204646514912191</v>
       </c>
       <c r="E23">
-        <v>-35.21095473472914</v>
+        <v>-35.88511318872503</v>
       </c>
       <c r="F23">
-        <v>-1.749375421338602</v>
+        <v>-2.462168175732117</v>
       </c>
       <c r="G23">
-        <v>-8.512201641972903</v>
+        <v>-9.315038730156019</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.072186692884201</v>
       </c>
       <c r="E24">
-        <v>-35.8545731600173</v>
+        <v>-36.73321938630355</v>
       </c>
       <c r="F24">
-        <v>-1.779173453552106</v>
+        <v>-2.069482265169817</v>
       </c>
       <c r="G24">
-        <v>-8.717935494510911</v>
+        <v>-8.761899539272431</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.96579972680746</v>
       </c>
       <c r="E25">
-        <v>-35.30312050197024</v>
+        <v>-36.74225595618586</v>
       </c>
       <c r="F25">
-        <v>-1.679537422343381</v>
+        <v>-1.725177981135425</v>
       </c>
       <c r="G25">
-        <v>-9.332991818615486</v>
+        <v>-9.249427028113203</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.894470782638299</v>
       </c>
       <c r="E26">
-        <v>-35.41668104466059</v>
+        <v>-36.16165124671443</v>
       </c>
       <c r="F26">
-        <v>-1.722904940982144</v>
+        <v>-1.81008729665718</v>
       </c>
       <c r="G26">
-        <v>-9.05724985955851</v>
+        <v>-9.173224890890259</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.866294712744009</v>
       </c>
       <c r="E27">
-        <v>-35.95333238541357</v>
+        <v>-36.87744901921085</v>
       </c>
       <c r="F27">
-        <v>-1.582842923781997</v>
+        <v>-1.866630827204872</v>
       </c>
       <c r="G27">
-        <v>-8.977555096791635</v>
+        <v>-9.667625072270557</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.884204195493359</v>
       </c>
       <c r="E28">
-        <v>-35.72467388310727</v>
+        <v>-37.20836952155837</v>
       </c>
       <c r="F28">
-        <v>-1.805599202068813</v>
+        <v>-1.867535404408729</v>
       </c>
       <c r="G28">
-        <v>-8.624127876110123</v>
+        <v>-9.604486347745578</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.953354149431023</v>
       </c>
       <c r="E29">
-        <v>-36.61263291619031</v>
+        <v>-35.68407837786551</v>
       </c>
       <c r="F29">
-        <v>-1.586288103810241</v>
+        <v>-1.441602968135071</v>
       </c>
       <c r="G29">
-        <v>-9.364885614340825</v>
+        <v>-9.000980517027518</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.079049551606631</v>
       </c>
       <c r="E30">
-        <v>-35.98933601801156</v>
+        <v>-37.42805258838147</v>
       </c>
       <c r="F30">
-        <v>-1.351047500395834</v>
+        <v>-1.896026272860615</v>
       </c>
       <c r="G30">
-        <v>-9.041107639509024</v>
+        <v>-9.456925401423643</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.259830829345352</v>
       </c>
       <c r="E31">
-        <v>-35.78658491550314</v>
+        <v>-36.52577452048618</v>
       </c>
       <c r="F31">
-        <v>-1.535676512233996</v>
+        <v>-1.792901158151299</v>
       </c>
       <c r="G31">
-        <v>-9.096529482381964</v>
+        <v>-10.05491255272774</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.494514238023036</v>
       </c>
       <c r="E32">
-        <v>-35.01184452532288</v>
+        <v>-35.29006943988013</v>
       </c>
       <c r="F32">
-        <v>-1.654903432518929</v>
+        <v>-1.861369865829692</v>
       </c>
       <c r="G32">
-        <v>-9.171129315563901</v>
+        <v>-9.821363496568772</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.78262681308414</v>
       </c>
       <c r="E33">
-        <v>-35.25458658179303</v>
+        <v>-35.89344558089914</v>
       </c>
       <c r="F33">
-        <v>-1.608915787785112</v>
+        <v>-1.799913288215997</v>
       </c>
       <c r="G33">
-        <v>-9.678973622379178</v>
+        <v>-9.528486153800529</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.1153045271489</v>
       </c>
       <c r="E34">
-        <v>-33.87075285215909</v>
+        <v>-34.8510972834726</v>
       </c>
       <c r="F34">
-        <v>-1.630321629840854</v>
+        <v>-1.845498346392054</v>
       </c>
       <c r="G34">
-        <v>-9.332117834593118</v>
+        <v>-9.897261063602103</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.483202416141372</v>
       </c>
       <c r="E35">
-        <v>-34.27642940342523</v>
+        <v>-34.34598223570904</v>
       </c>
       <c r="F35">
-        <v>-1.430159072465395</v>
+        <v>-1.736044504725349</v>
       </c>
       <c r="G35">
-        <v>-9.515975602207623</v>
+        <v>-10.23266567436782</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.879813636860707</v>
       </c>
       <c r="E36">
-        <v>-33.51376871766043</v>
+        <v>-34.90513103533213</v>
       </c>
       <c r="F36">
-        <v>-1.486942001192496</v>
+        <v>-1.499170360792622</v>
       </c>
       <c r="G36">
-        <v>-10.02759724148321</v>
+        <v>-9.746502130289233</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.2919628234075</v>
       </c>
       <c r="E37">
-        <v>-33.36897528973918</v>
+        <v>-33.83300802130515</v>
       </c>
       <c r="F37">
-        <v>-1.779643966236896</v>
+        <v>-1.774182539950238</v>
       </c>
       <c r="G37">
-        <v>-10.03970059597479</v>
+        <v>-10.63031185181738</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.708786010705729</v>
       </c>
       <c r="E38">
-        <v>-32.67662369141747</v>
+        <v>-32.6898106077278</v>
       </c>
       <c r="F38">
-        <v>-1.689357717903569</v>
+        <v>-1.864680850338682</v>
       </c>
       <c r="G38">
-        <v>-10.23781688322693</v>
+        <v>-10.6749247635046</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.125017597275409</v>
       </c>
       <c r="E39">
-        <v>-31.69354179756631</v>
+        <v>-31.53748605478799</v>
       </c>
       <c r="F39">
-        <v>-1.234555020907543</v>
+        <v>-1.357652073698355</v>
       </c>
       <c r="G39">
-        <v>-10.21764572925615</v>
+        <v>-10.72983347181895</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.529013471121035</v>
       </c>
       <c r="E40">
-        <v>-31.34656559062461</v>
+        <v>-31.94462077468459</v>
       </c>
       <c r="F40">
-        <v>-1.292232586429666</v>
+        <v>-1.51320124786124</v>
       </c>
       <c r="G40">
-        <v>-10.41019367891124</v>
+        <v>-10.44551388926973</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.912385450131101</v>
       </c>
       <c r="E41">
-        <v>-31.29173935581374</v>
+        <v>-31.1436446703409</v>
       </c>
       <c r="F41">
-        <v>-1.281764507560489</v>
+        <v>-1.431875449723996</v>
       </c>
       <c r="G41">
-        <v>-9.714131616006238</v>
+        <v>-10.35841012558596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.272654251779374</v>
       </c>
       <c r="E42">
-        <v>-30.85763757320146</v>
+        <v>-31.33998118941745</v>
       </c>
       <c r="F42">
-        <v>-1.271314652774173</v>
+        <v>-1.459450143828386</v>
       </c>
       <c r="G42">
-        <v>-10.21273950076695</v>
+        <v>-10.29734049202303</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.602215273047925</v>
       </c>
       <c r="E43">
-        <v>-30.39051189388824</v>
+        <v>-30.44171082101896</v>
       </c>
       <c r="F43">
-        <v>-1.308718754480182</v>
+        <v>-1.372603276951483</v>
       </c>
       <c r="G43">
-        <v>-10.2597492474246</v>
+        <v>-10.82220100291016</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.898850939985486</v>
       </c>
       <c r="E44">
-        <v>-29.29563782644673</v>
+        <v>-30.34147078462217</v>
       </c>
       <c r="F44">
-        <v>-1.039453788363189</v>
+        <v>-1.201643155626915</v>
       </c>
       <c r="G44">
-        <v>-10.43806185126083</v>
+        <v>-10.6739547736616</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.165787401728</v>
       </c>
       <c r="E45">
-        <v>-28.70556407782526</v>
+        <v>-28.95612907314367</v>
       </c>
       <c r="F45">
-        <v>-1.170549556795433</v>
+        <v>-1.190411322012357</v>
       </c>
       <c r="G45">
-        <v>-10.12054080749825</v>
+        <v>-10.3281418077204</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.40088472139902</v>
       </c>
       <c r="E46">
-        <v>-27.50004806919135</v>
+        <v>-29.38431893293894</v>
       </c>
       <c r="F46">
-        <v>-1.081259006080272</v>
+        <v>-1.153832274239536</v>
       </c>
       <c r="G46">
-        <v>-10.90287237661112</v>
+        <v>-10.93989420737679</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.60701657459574</v>
       </c>
       <c r="E47">
-        <v>-27.37964047380141</v>
+        <v>-28.59734713446396</v>
       </c>
       <c r="F47">
-        <v>-0.8160273608475092</v>
+        <v>-0.9577775908145605</v>
       </c>
       <c r="G47">
-        <v>-10.80238738785762</v>
+        <v>-10.99748445757795</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.78923642906572</v>
       </c>
       <c r="E48">
-        <v>-26.29026170956821</v>
+        <v>-28.57671993535902</v>
       </c>
       <c r="F48">
-        <v>-0.5761893183475655</v>
+        <v>-0.7828711271830561</v>
       </c>
       <c r="G48">
-        <v>-10.88536952234499</v>
+        <v>-10.17889248317344</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.9459994805291</v>
       </c>
       <c r="E49">
-        <v>-26.71580241206899</v>
+        <v>-27.2173399653665</v>
       </c>
       <c r="F49">
-        <v>-0.7045904076185029</v>
+        <v>-0.9326482372832348</v>
       </c>
       <c r="G49">
-        <v>-10.47173009939521</v>
+        <v>-10.25933873977773</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.08048933018816</v>
       </c>
       <c r="E50">
-        <v>-25.60933318693085</v>
+        <v>-26.74849799440437</v>
       </c>
       <c r="F50">
-        <v>-0.816313147601475</v>
+        <v>-1.162622909118045</v>
       </c>
       <c r="G50">
-        <v>-10.56961299935485</v>
+        <v>-10.37396306852946</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.19556138431366</v>
       </c>
       <c r="E51">
-        <v>-24.67747739105446</v>
+        <v>-25.54035547084601</v>
       </c>
       <c r="F51">
-        <v>-0.5407269098337186</v>
+        <v>-0.577942972139292</v>
       </c>
       <c r="G51">
-        <v>-10.55343105275889</v>
+        <v>-10.82929881254636</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.28814368010856</v>
       </c>
       <c r="E52">
-        <v>-25.26263774537761</v>
+        <v>-24.70827101430662</v>
       </c>
       <c r="F52">
-        <v>-0.7657769374588855</v>
+        <v>-0.9518133455144041</v>
       </c>
       <c r="G52">
-        <v>-10.52176237413022</v>
+        <v>-10.87993691711505</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.36071757056421</v>
       </c>
       <c r="E53">
-        <v>-24.78938504073201</v>
+        <v>-24.42426776691558</v>
       </c>
       <c r="F53">
-        <v>-0.8326841725830015</v>
+        <v>-0.8779776454332729</v>
       </c>
       <c r="G53">
-        <v>-11.1672095062853</v>
+        <v>-11.36611039283026</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.41486390774714</v>
       </c>
       <c r="E54">
-        <v>-23.730813485173</v>
+        <v>-24.41009817174557</v>
       </c>
       <c r="F54">
-        <v>-0.8224248422993297</v>
+        <v>-0.8093316671306807</v>
       </c>
       <c r="G54">
-        <v>-10.62212818324431</v>
+        <v>-11.05998755735939</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.44848343705476</v>
       </c>
       <c r="E55">
-        <v>-23.69714880939998</v>
+        <v>-24.37638821123248</v>
       </c>
       <c r="F55">
-        <v>-0.8815901556768816</v>
+        <v>-1.024025445486048</v>
       </c>
       <c r="G55">
-        <v>-11.11211209687522</v>
+        <v>-11.00821724621627</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.46622006181776</v>
       </c>
       <c r="E56">
-        <v>-22.58591562960576</v>
+        <v>-23.31439765779767</v>
       </c>
       <c r="F56">
-        <v>-0.8745506894878914</v>
+        <v>-0.8894058021222949</v>
       </c>
       <c r="G56">
-        <v>-10.81680812422669</v>
+        <v>-11.08408832888528</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.47078437855262</v>
       </c>
       <c r="E57">
-        <v>-21.80497123003499</v>
+        <v>-23.09119370243361</v>
       </c>
       <c r="F57">
-        <v>-0.8661502156561016</v>
+        <v>-0.5646841234900831</v>
       </c>
       <c r="G57">
-        <v>-10.55545048553784</v>
+        <v>-11.58253730746011</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.46210548736757</v>
       </c>
       <c r="E58">
-        <v>-21.41708478890799</v>
+        <v>-23.24011709864985</v>
       </c>
       <c r="F58">
-        <v>-0.6870323321487645</v>
+        <v>-1.086130634776135</v>
       </c>
       <c r="G58">
-        <v>-10.9063186545175</v>
+        <v>-11.58710917084984</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.44645571910887</v>
       </c>
       <c r="E59">
-        <v>-21.52807315836198</v>
+        <v>-22.06145946935544</v>
       </c>
       <c r="F59">
-        <v>-0.8216238110208226</v>
+        <v>-1.037049037792862</v>
       </c>
       <c r="G59">
-        <v>-10.91591923658139</v>
+        <v>-11.39520015648383</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.42596925482442</v>
       </c>
       <c r="E60">
-        <v>-21.36452279110096</v>
+        <v>-21.53742445718782</v>
       </c>
       <c r="F60">
-        <v>-0.9790749167405358</v>
+        <v>-0.9870148182963691</v>
       </c>
       <c r="G60">
-        <v>-10.96830199864927</v>
+        <v>-11.57580365783323</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.40008214055775</v>
       </c>
       <c r="E61">
-        <v>-20.10497303060753</v>
+        <v>-21.635533846564</v>
       </c>
       <c r="F61">
-        <v>-0.9826476653488101</v>
+        <v>-1.124032585291227</v>
       </c>
       <c r="G61">
-        <v>-11.11886229922979</v>
+        <v>-11.49374516555132</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.37360082014828</v>
       </c>
       <c r="E62">
-        <v>-20.45519615341274</v>
+        <v>-21.23981314540373</v>
       </c>
       <c r="F62">
-        <v>-1.333608709832099</v>
+        <v>-1.478872045954423</v>
       </c>
       <c r="G62">
-        <v>-10.59137652573001</v>
+        <v>-12.01770189750623</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.34516487302911</v>
       </c>
       <c r="E63">
-        <v>-20.68943147145949</v>
+        <v>-21.56581798921592</v>
       </c>
       <c r="F63">
-        <v>-1.078682783457565</v>
+        <v>-1.655255488665119</v>
       </c>
       <c r="G63">
-        <v>-11.32073605566901</v>
+        <v>-11.75727452211392</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.31119214945867</v>
       </c>
       <c r="E64">
-        <v>-20.84440038047597</v>
+        <v>-20.0776799177633</v>
       </c>
       <c r="F64">
-        <v>-1.355208389860096</v>
+        <v>-1.375452860817113</v>
       </c>
       <c r="G64">
-        <v>-11.21135894159703</v>
+        <v>-11.85070473832323</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.27402068629203</v>
       </c>
       <c r="E65">
-        <v>-19.33396410300959</v>
+        <v>-20.89598875637136</v>
       </c>
       <c r="F65">
-        <v>-1.484148746310256</v>
+        <v>-1.565209466878604</v>
       </c>
       <c r="G65">
-        <v>-11.45458472236728</v>
+        <v>-12.32875744583061</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.23013904295059</v>
       </c>
       <c r="E66">
-        <v>-19.41138742311873</v>
+        <v>-20.34514970655234</v>
       </c>
       <c r="F66">
-        <v>-1.529313822213094</v>
+        <v>-1.662841677339957</v>
       </c>
       <c r="G66">
-        <v>-11.51052632088988</v>
+        <v>-12.00067245125222</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.17627060825274</v>
       </c>
       <c r="E67">
-        <v>-19.47664273356926</v>
+        <v>-20.33861511855927</v>
       </c>
       <c r="F67">
-        <v>-1.624613350068163</v>
+        <v>-1.621205446573045</v>
       </c>
       <c r="G67">
-        <v>-11.47835112879371</v>
+        <v>-11.52903558099995</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.11460801848217</v>
       </c>
       <c r="E68">
-        <v>-19.43750313272096</v>
+        <v>-20.120600794408</v>
       </c>
       <c r="F68">
-        <v>-1.872001133077221</v>
+        <v>-1.736553950678071</v>
       </c>
       <c r="G68">
-        <v>-11.38138193940292</v>
+        <v>-11.90104489379339</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.0401339032714</v>
       </c>
       <c r="E69">
-        <v>-18.97709770883512</v>
+        <v>-20.18776712088976</v>
       </c>
       <c r="F69">
-        <v>-1.978548233527502</v>
+        <v>-1.997358800510273</v>
       </c>
       <c r="G69">
-        <v>-11.47572255563553</v>
+        <v>-11.28380029908736</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.94816990762497</v>
       </c>
       <c r="E70">
-        <v>-19.08818570471729</v>
+        <v>-19.42072966499655</v>
       </c>
       <c r="F70">
-        <v>-2.070488731564219</v>
+        <v>-2.157679370913284</v>
       </c>
       <c r="G70">
-        <v>-11.265350628797</v>
+        <v>-11.37297977482424</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.83869547589262</v>
       </c>
       <c r="E71">
-        <v>-19.09732869373877</v>
+        <v>-19.38208366781509</v>
       </c>
       <c r="F71">
-        <v>-2.05137415374462</v>
+        <v>-2.249018474215568</v>
       </c>
       <c r="G71">
-        <v>-10.80986259968529</v>
+        <v>-11.42461104305472</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.70471326407652</v>
       </c>
       <c r="E72">
-        <v>-18.71363561954287</v>
+        <v>-19.59057008265423</v>
       </c>
       <c r="F72">
-        <v>-2.18556967299814</v>
+        <v>-2.262093425301356</v>
       </c>
       <c r="G72">
-        <v>-11.43638003244683</v>
+        <v>-10.97122852090599</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.54272166955793</v>
       </c>
       <c r="E73">
-        <v>-19.00888759636897</v>
+        <v>-19.76532842308423</v>
       </c>
       <c r="F73">
-        <v>-2.23417661545961</v>
+        <v>-2.195051166290583</v>
       </c>
       <c r="G73">
-        <v>-10.72939316926223</v>
+        <v>-11.31335353911643</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.35459409622812</v>
       </c>
       <c r="E74">
-        <v>-19.30778952324525</v>
+        <v>-19.92589905444821</v>
       </c>
       <c r="F74">
-        <v>-2.358954425710702</v>
+        <v>-2.343526911200964</v>
       </c>
       <c r="G74">
-        <v>-11.29765162162367</v>
+        <v>-11.42544198998508</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.13560317283952</v>
       </c>
       <c r="E75">
-        <v>-19.99587303481473</v>
+        <v>-20.31953665756496</v>
       </c>
       <c r="F75">
-        <v>-2.190381659241003</v>
+        <v>-2.721671660374521</v>
       </c>
       <c r="G75">
-        <v>-10.28618395355568</v>
+        <v>-10.71494594852885</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.886574582516072</v>
       </c>
       <c r="E76">
-        <v>-19.5100809856419</v>
+        <v>-20.12435037088635</v>
       </c>
       <c r="F76">
-        <v>-2.405402642720476</v>
+        <v>-2.504766969421082</v>
       </c>
       <c r="G76">
-        <v>-10.86811495899431</v>
+        <v>-10.641322726281</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.61254868866537</v>
       </c>
       <c r="E77">
-        <v>-19.57560347605888</v>
+        <v>-21.5189301693405</v>
       </c>
       <c r="F77">
-        <v>-2.731330424291164</v>
+        <v>-2.621648781588689</v>
       </c>
       <c r="G77">
-        <v>-10.35624833934882</v>
+        <v>-10.55652972338365</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.311480296381289</v>
       </c>
       <c r="E78">
-        <v>-19.75549257753957</v>
+        <v>-20.96921870954939</v>
       </c>
       <c r="F78">
-        <v>-2.595971877204113</v>
+        <v>-2.734795485137074</v>
       </c>
       <c r="G78">
-        <v>-10.33092928706447</v>
+        <v>-10.52046795082437</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.987480616332562</v>
       </c>
       <c r="E79">
-        <v>-20.99586877908453</v>
+        <v>-20.87523023152019</v>
       </c>
       <c r="F79">
-        <v>-2.669950884845929</v>
+        <v>-2.870846547372865</v>
       </c>
       <c r="G79">
-        <v>-9.858362153515667</v>
+        <v>-10.48598861903286</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.646535295756195</v>
       </c>
       <c r="E80">
-        <v>-20.90124178622025</v>
+        <v>-21.40127135767321</v>
       </c>
       <c r="F80">
-        <v>-2.628728837780417</v>
+        <v>-3.008054838870367</v>
       </c>
       <c r="G80">
-        <v>-9.861828294695284</v>
+        <v>-10.05762057897886</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.286479449487343</v>
       </c>
       <c r="E81">
-        <v>-21.10001915278694</v>
+        <v>-21.54539457144132</v>
       </c>
       <c r="F81">
-        <v>-3.044083850687728</v>
+        <v>-2.703453376084752</v>
       </c>
       <c r="G81">
-        <v>-9.108692426693246</v>
+        <v>-9.961763732889263</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.91230834831345</v>
       </c>
       <c r="E82">
-        <v>-21.79845022746395</v>
+        <v>-22.56753002513462</v>
       </c>
       <c r="F82">
-        <v>-2.711674922557537</v>
+        <v>-2.592988097819229</v>
       </c>
       <c r="G82">
-        <v>-9.63863462498316</v>
+        <v>-9.509119462395793</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.530585819783756</v>
       </c>
       <c r="E83">
-        <v>-22.24077345463716</v>
+        <v>-22.96493984709976</v>
       </c>
       <c r="F83">
-        <v>-2.921402638333122</v>
+        <v>-3.204881560714751</v>
       </c>
       <c r="G83">
-        <v>-9.118213555664189</v>
+        <v>-9.656607576715862</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.141237838295023</v>
       </c>
       <c r="E84">
-        <v>-23.08469081375859</v>
+        <v>-23.59814278217028</v>
       </c>
       <c r="F84">
-        <v>-3.376621175765353</v>
+        <v>-2.923327764177227</v>
       </c>
       <c r="G84">
-        <v>-8.859335515584261</v>
+        <v>-8.859004461030334</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.752497462733172</v>
       </c>
       <c r="E85">
-        <v>-22.88198726022725</v>
+        <v>-24.66011522170906</v>
       </c>
       <c r="F85">
-        <v>-2.911198808665437</v>
+        <v>-3.18849148328296</v>
       </c>
       <c r="G85">
-        <v>-9.18398085334735</v>
+        <v>-8.943532620284545</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.37363472543317</v>
       </c>
       <c r="E86">
-        <v>-24.6127337981668</v>
+        <v>-25.82105746068547</v>
       </c>
       <c r="F86">
-        <v>-3.5425448232809</v>
+        <v>-3.024945250213448</v>
       </c>
       <c r="G86">
-        <v>-8.865102485913672</v>
+        <v>-9.311953301713418</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.007868956375942</v>
       </c>
       <c r="E87">
-        <v>-25.23714696518843</v>
+        <v>-26.57644768143095</v>
       </c>
       <c r="F87">
-        <v>-3.088825630847735</v>
+        <v>-3.355187169217916</v>
       </c>
       <c r="G87">
-        <v>-8.264331165811051</v>
+        <v>-9.387870732019985</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.665818636135722</v>
       </c>
       <c r="E88">
-        <v>-25.68517606961131</v>
+        <v>-26.61533821620882</v>
       </c>
       <c r="F88">
-        <v>-3.480375021333394</v>
+        <v>-3.423944148752483</v>
       </c>
       <c r="G88">
-        <v>-8.870581438781166</v>
+        <v>-9.42000288702415</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.358977803238592</v>
       </c>
       <c r="E89">
-        <v>-27.93447816616919</v>
+        <v>-28.58113972599051</v>
       </c>
       <c r="F89">
-        <v>-3.506296294101796</v>
+        <v>-3.345863065732005</v>
       </c>
       <c r="G89">
-        <v>-8.579203773142211</v>
+        <v>-8.680122443361356</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.092386550598989</v>
       </c>
       <c r="E90">
-        <v>-28.6525130048254</v>
+        <v>-28.94781932333959</v>
       </c>
       <c r="F90">
-        <v>-3.372914231637826</v>
+        <v>-3.662692059750343</v>
       </c>
       <c r="G90">
-        <v>-8.515085127137608</v>
+        <v>-8.44257755873649</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.875040718633366</v>
       </c>
       <c r="E91">
-        <v>-29.65021960548432</v>
+        <v>-30.73287811429014</v>
       </c>
       <c r="F91">
-        <v>-3.839216324919515</v>
+        <v>-3.575510532442709</v>
       </c>
       <c r="G91">
-        <v>-8.527678442368995</v>
+        <v>-8.650678451335077</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.715258602485582</v>
       </c>
       <c r="E92">
-        <v>-31.54133978616852</v>
+        <v>-32.61615044951904</v>
       </c>
       <c r="F92">
-        <v>-3.599896840413724</v>
+        <v>-3.633381107569685</v>
       </c>
       <c r="G92">
-        <v>-8.748058148372738</v>
+        <v>-8.997087315473335</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.612634268681389</v>
       </c>
       <c r="E93">
-        <v>-32.71763128779393</v>
+        <v>-34.4306805493115</v>
       </c>
       <c r="F93">
-        <v>-3.781600058585198</v>
+        <v>-4.078089319395197</v>
       </c>
       <c r="G93">
-        <v>-8.425379274659976</v>
+        <v>-8.771904007892109</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.567529268568733</v>
       </c>
       <c r="E94">
-        <v>-34.16934005009184</v>
+        <v>-34.72134744620483</v>
       </c>
       <c r="F94">
-        <v>-3.724610866374801</v>
+        <v>-4.330487896823789</v>
       </c>
       <c r="G94">
-        <v>-9.232774984050669</v>
+        <v>-9.322758922353598</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.579198985649893</v>
       </c>
       <c r="E95">
-        <v>-36.38848703823265</v>
+        <v>-35.51801244329323</v>
       </c>
       <c r="F95">
-        <v>-4.048424654333544</v>
+        <v>-4.00373423295251</v>
       </c>
       <c r="G95">
-        <v>-9.065307727401096</v>
+        <v>-9.394514996917302</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.638822487815688</v>
       </c>
       <c r="E96">
-        <v>-37.14771287646263</v>
+        <v>-37.55729750079738</v>
       </c>
       <c r="F96">
-        <v>-4.03952301822306</v>
+        <v>-4.068486056094542</v>
       </c>
       <c r="G96">
-        <v>-9.902097770634978</v>
+        <v>-9.797643437779893</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.735482344819702</v>
       </c>
       <c r="E97">
-        <v>-38.83832581350919</v>
+        <v>-39.65185031932815</v>
       </c>
       <c r="F97">
-        <v>-4.005400908166943</v>
+        <v>-4.349604131378194</v>
       </c>
       <c r="G97">
-        <v>-9.70435888557431</v>
+        <v>-9.609253533322127</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.86217883780213</v>
       </c>
       <c r="E98">
-        <v>-41.32851555643109</v>
+        <v>-41.0725254492515</v>
       </c>
       <c r="F98">
-        <v>-4.254099996774634</v>
+        <v>-4.699148667602696</v>
       </c>
       <c r="G98">
-        <v>-10.42059872354117</v>
+        <v>-9.95310334575853</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.997823001183528</v>
       </c>
       <c r="E99">
-        <v>-42.86649401281213</v>
+        <v>-42.39920304419763</v>
       </c>
       <c r="F99">
-        <v>-4.568631099617606</v>
+        <v>-4.835020802479482</v>
       </c>
       <c r="G99">
-        <v>-10.28926938199828</v>
+        <v>-10.35399716838211</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.13446701846382</v>
       </c>
       <c r="E100">
-        <v>-44.86397899098849</v>
+        <v>-45.49786119716016</v>
       </c>
       <c r="F100">
-        <v>-4.406976857696088</v>
+        <v>-5.0380710486211</v>
       </c>
       <c r="G100">
-        <v>-10.42235662322252</v>
+        <v>-11.04970831345995</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.249160854784011</v>
       </c>
       <c r="E101">
-        <v>-46.56091594198677</v>
+        <v>-46.40810032236093</v>
       </c>
       <c r="F101">
-        <v>-4.856571608830714</v>
+        <v>-4.794046437267407</v>
       </c>
       <c r="G101">
-        <v>-10.66402644758932</v>
+        <v>-10.48551521102074</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.344079138812862</v>
       </c>
       <c r="E102">
-        <v>-48.80002217931638</v>
+        <v>-48.31508601173099</v>
       </c>
       <c r="F102">
-        <v>-4.832300443928689</v>
+        <v>-5.216855100065108</v>
       </c>
       <c r="G102">
-        <v>-11.19965947366124</v>
+        <v>-11.57121855226134</v>
       </c>
     </row>
   </sheetData>
